--- a/Thread Chart/Logomark Thread Charts.xlsx
+++ b/Thread Chart/Logomark Thread Charts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\fs1\InformationManagement\Procedures &amp; References\Embroidery Thread Charts\Completed\Logomark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C56174-8E9E-46D6-99EF-F1A81086D099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE280607-816C-4032-8839-D90DF59B2E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22920" yWindow="-1095" windowWidth="29040" windowHeight="15840" xr2:uid="{F028543A-CA1A-4C22-838B-894A262A5CAB}"/>
+    <workbookView xWindow="19090" yWindow="-5720" windowWidth="38620" windowHeight="21100" xr2:uid="{F028543A-CA1A-4C22-838B-894A262A5CAB}"/>
   </bookViews>
   <sheets>
     <sheet name="Gunold Polyester" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gunold Polyester'!$A$1:$I$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -29,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -50,6 +53,9 @@
     <t>Thread Number</t>
   </si>
   <si>
+    <t>Monitor Display Color</t>
+  </si>
+  <si>
     <t>PMS Number</t>
   </si>
   <si>
@@ -62,19 +68,49 @@
     <t>B</t>
   </si>
   <si>
-    <t>Monitor Display Color</t>
-  </si>
-  <si>
     <t>NA</t>
   </si>
   <si>
-    <t>Yellows</t>
+    <t>Blacks</t>
+  </si>
+  <si>
+    <t>Gunold Polyester</t>
+  </si>
+  <si>
+    <t>Black 4</t>
+  </si>
+  <si>
+    <t>Black 6</t>
+  </si>
+  <si>
+    <t>Blues</t>
+  </si>
+  <si>
+    <t>Browns</t>
+  </si>
+  <si>
+    <t>Grays</t>
+  </si>
+  <si>
+    <t>Warm Gray 1</t>
+  </si>
+  <si>
+    <t>Cool Gray 4</t>
+  </si>
+  <si>
+    <t>Cool Gray 5</t>
+  </si>
+  <si>
+    <t>Cool Gray 10</t>
+  </si>
+  <si>
+    <t>Greens</t>
   </si>
   <si>
     <t>Oranges</t>
   </si>
   <si>
-    <t>Reds</t>
+    <t>Orange 21</t>
   </si>
   <si>
     <t>Pinks</t>
@@ -83,52 +119,19 @@
     <t>Purples</t>
   </si>
   <si>
-    <t>Blues</t>
-  </si>
-  <si>
-    <t>Greens</t>
-  </si>
-  <si>
-    <t>Browns</t>
-  </si>
-  <si>
-    <t>Grays</t>
-  </si>
-  <si>
-    <t>Blacks</t>
-  </si>
-  <si>
-    <t>Warm Gray 1</t>
-  </si>
-  <si>
-    <t>Cool Gray 5</t>
+    <t>Reds</t>
   </si>
   <si>
     <t>Warm Red</t>
-  </si>
-  <si>
-    <t>Cool Gray 10</t>
-  </si>
-  <si>
-    <t>Gunold Polyester</t>
-  </si>
-  <si>
-    <t>Orange 21</t>
-  </si>
-  <si>
-    <t>Black 4</t>
-  </si>
-  <si>
-    <t>Black 6</t>
-  </si>
-  <si>
-    <t>Cool Gray 4</t>
   </si>
   <si>
     <t>White</t>
   </si>
   <si>
     <t>Trans. White</t>
+  </si>
+  <si>
+    <t>Yellows</t>
   </si>
 </sst>
 </file>
@@ -138,7 +141,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2137,8 +2140,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE7DE5AC-E6A0-4E0D-9AE8-E8E89420A822}">
-  <dimension ref="A1:I407"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O407"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" style="1" customWidth="1"/>
@@ -2146,14 +2149,14 @@
     <col min="4" max="4" width="19.7109375" style="17" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.7109375" style="1" customWidth="1"/>
-    <col min="7" max="9" width="8.85546875" style="1"/>
-    <col min="10" max="10" width="20.7109375" style="1" customWidth="1"/>
-    <col min="11" max="14" width="8.85546875" style="1"/>
-    <col min="15" max="15" width="50.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.85546875" style="1"/>
+    <col min="7" max="9" width="8.85546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="14" width="8.85546875" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="50.7109375" style="1" hidden="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="1" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="2" customFormat="1" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="2" customFormat="1" ht="50.1" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2167,37 +2170,37 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:9" ht="50.1" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D2" s="17">
         <v>61130</v>
       </c>
       <c r="E2" s="176"/>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G2" s="1">
         <v>48</v>
@@ -2209,22 +2212,22 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="50.1" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D3" s="17">
         <v>61352</v>
       </c>
       <c r="E3" s="177"/>
       <c r="F3" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="G3" s="1">
         <v>16</v>
@@ -2236,15 +2239,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="50.1" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D4" s="17">
         <v>61151</v>
@@ -2263,15 +2266,15 @@
         <v>230</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="50.1" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D5" s="17">
         <v>61074</v>
@@ -2290,15 +2293,15 @@
         <v>234</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="50.1" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D6" s="17">
         <v>61236</v>
@@ -2317,15 +2320,15 @@
         <v>218</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="50.1" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D7" s="17">
         <v>61459</v>
@@ -2344,15 +2347,15 @@
         <v>234</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="50.1" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D8" s="17">
         <v>61028</v>
@@ -2371,15 +2374,15 @@
         <v>226</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="50.1" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D9" s="17">
         <v>61222</v>
@@ -2398,15 +2401,15 @@
         <v>233</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="50.1" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D10" s="17">
         <v>61145</v>
@@ -2425,15 +2428,15 @@
         <v>232</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="50.1" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D11" s="17">
         <v>61433</v>
@@ -2452,15 +2455,15 @@
         <v>232</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="50.1" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D12" s="17">
         <v>61431</v>
@@ -2479,15 +2482,15 @@
         <v>233</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="50.1" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D13" s="17">
         <v>61029</v>
@@ -2506,15 +2509,15 @@
         <v>228</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="50.1" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D14" s="17">
         <v>61249</v>
@@ -2533,15 +2536,15 @@
         <v>229</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="50.1" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D15" s="17">
         <v>61030</v>
@@ -2560,15 +2563,15 @@
         <v>220</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="50.1" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D16" s="17">
         <v>61437</v>
@@ -2587,15 +2590,15 @@
         <v>226</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="50.1" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D17" s="17">
         <v>61095</v>
@@ -2614,15 +2617,15 @@
         <v>215</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="50.1" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D18" s="17">
         <v>61440</v>
@@ -2641,15 +2644,15 @@
         <v>200</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="50.1" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D19" s="17">
         <v>61430</v>
@@ -2668,15 +2671,15 @@
         <v>222</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="50.1" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D20" s="17">
         <v>61094</v>
@@ -2695,15 +2698,15 @@
         <v>205</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="50.1" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
         <v>61196</v>
@@ -2722,15 +2725,15 @@
         <v>220</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="50.1" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D22" s="17">
         <v>61252</v>
@@ -2749,15 +2752,15 @@
         <v>200</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="50.1" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D23" s="17">
         <v>61468</v>
@@ -2776,15 +2779,15 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="50.1" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D24" s="17">
         <v>61466</v>
@@ -2803,15 +2806,15 @@
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="50.1" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D25" s="17">
         <v>61428</v>
@@ -2830,15 +2833,15 @@
         <v>204</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="50.1" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D26" s="17">
         <v>61435</v>
@@ -2857,15 +2860,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="50.1" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D27" s="17">
         <v>61143</v>
@@ -2884,15 +2887,15 @@
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="50.1" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D28" s="17">
         <v>61198</v>
@@ -2911,15 +2914,15 @@
         <v>147</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="50.1" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D29" s="17">
         <v>61425</v>
@@ -2938,15 +2941,15 @@
         <v>159</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="50.1" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D30" s="17">
         <v>61535</v>
@@ -2965,15 +2968,15 @@
         <v>147</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="50.1" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D31" s="17">
         <v>61426</v>
@@ -2992,15 +2995,15 @@
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="50.1" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D32" s="17">
         <v>61200</v>
@@ -3019,15 +3022,15 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="50.1" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D33" s="17">
         <v>61460</v>
@@ -3046,15 +3049,15 @@
         <v>114</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="50.1" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D34" s="17">
         <v>61424</v>
@@ -3073,15 +3076,15 @@
         <v>108</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="50.1" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D35" s="17">
         <v>61424</v>
@@ -3100,15 +3103,15 @@
         <v>108</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="50.1" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D36" s="17">
         <v>61438</v>
@@ -3127,15 +3130,15 @@
         <v>91</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="50.1" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D37" s="17">
         <v>61427</v>
@@ -3154,15 +3157,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="50.1" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D38" s="17">
         <v>61042</v>
@@ -3181,15 +3184,15 @@
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="50.1" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D39" s="17">
         <v>61467</v>
@@ -3208,15 +3211,15 @@
         <v>104</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="50.1" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D40" s="17">
         <v>61235</v>
@@ -3235,15 +3238,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="50.1" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D41" s="17">
         <v>61044</v>
@@ -3262,15 +3265,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="50.1" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D42" s="17">
         <v>61422</v>
@@ -3289,15 +3292,15 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="50.1" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D43" s="17">
         <v>61461</v>
@@ -3316,15 +3319,15 @@
         <v>67</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="50.1" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D44" s="17">
         <v>61436</v>
@@ -3343,15 +3346,15 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="50.1" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D45" s="17">
         <v>61420</v>
@@ -3370,15 +3373,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="50.1" customHeight="1">
       <c r="A46" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D46" s="17">
         <v>61220</v>
@@ -3397,15 +3400,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="50.1" customHeight="1">
       <c r="A47" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D47" s="17">
         <v>61419</v>
@@ -3424,15 +3427,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="50.1" customHeight="1">
       <c r="A48" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D48" s="17">
         <v>61476</v>
@@ -3451,15 +3454,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="50.1" customHeight="1">
       <c r="A49" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D49" s="17">
         <v>61017</v>
@@ -3478,15 +3481,15 @@
         <v>165</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="50.1" customHeight="1">
       <c r="A50" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D50" s="17">
         <v>61378</v>
@@ -3505,15 +3508,15 @@
         <v>164</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="50.1" customHeight="1">
       <c r="A51" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D51" s="17">
         <v>61082</v>
@@ -3532,15 +3535,15 @@
         <v>161</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="50.1" customHeight="1">
       <c r="A52" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D52" s="17">
         <v>61462</v>
@@ -3559,15 +3562,15 @@
         <v>156</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="50.1" customHeight="1">
       <c r="A53" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D53" s="17">
         <v>61127</v>
@@ -3586,15 +3589,15 @@
         <v>138</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="50.1" customHeight="1">
       <c r="A54" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D54" s="17">
         <v>61055</v>
@@ -3613,15 +3616,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="50.1" customHeight="1">
       <c r="A55" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D55" s="17">
         <v>61381</v>
@@ -3640,15 +3643,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="50.1" customHeight="1">
       <c r="A56" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D56" s="17">
         <v>61126</v>
@@ -3667,15 +3670,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="50.1" customHeight="1">
       <c r="A57" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D57" s="17">
         <v>61364</v>
@@ -3694,15 +3697,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="50.1" customHeight="1">
       <c r="A58" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D58" s="17">
         <v>61383</v>
@@ -3721,15 +3724,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="50.1" customHeight="1">
       <c r="A59" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D59" s="17">
         <v>61377</v>
@@ -3748,15 +3751,15 @@
         <v>92</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="50.1" customHeight="1">
       <c r="A60" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D60" s="17">
         <v>61389</v>
@@ -3775,15 +3778,15 @@
         <v>92</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="50.1" customHeight="1">
       <c r="A61" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D61" s="17">
         <v>61384</v>
@@ -3802,15 +3805,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="50.1" customHeight="1">
       <c r="A62" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D62" s="17">
         <v>61158</v>
@@ -3829,15 +3832,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="50.1" customHeight="1">
       <c r="A63" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D63" s="17">
         <v>61360</v>
@@ -3856,15 +3859,15 @@
         <v>23</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="50.1" customHeight="1">
       <c r="A64" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D64" s="17">
         <v>61170</v>
@@ -3883,15 +3886,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="50.1" customHeight="1">
       <c r="A65" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D65" s="17">
         <v>61382</v>
@@ -3910,15 +3913,15 @@
         <v>37</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="50.1" customHeight="1">
       <c r="A66" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D66" s="17">
         <v>61036</v>
@@ -3937,15 +3940,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="50.1" customHeight="1">
       <c r="A67" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D67" s="17">
         <v>61057</v>
@@ -3964,15 +3967,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="50.1" customHeight="1">
       <c r="A68" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D68" s="17">
         <v>61386</v>
@@ -3991,15 +3994,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="50.1" customHeight="1">
       <c r="A69" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D69" s="17">
         <v>61214</v>
@@ -4018,15 +4021,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="50.1" customHeight="1">
       <c r="A70" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D70" s="17">
         <v>61129</v>
@@ -4045,22 +4048,22 @@
         <v>44</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="50.1" customHeight="1">
       <c r="A71" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D71" s="17">
         <v>61086</v>
       </c>
       <c r="E71" s="182"/>
       <c r="F71" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G71" s="1">
         <v>215</v>
@@ -4072,22 +4075,22 @@
         <v>202</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="50.1" customHeight="1">
       <c r="A72" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D72" s="17">
         <v>61474</v>
       </c>
       <c r="E72" s="182"/>
       <c r="F72" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G72" s="1">
         <v>215</v>
@@ -4099,15 +4102,15 @@
         <v>202</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="50.1" customHeight="1">
       <c r="A73" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D73" s="17">
         <v>61085</v>
@@ -4126,15 +4129,15 @@
         <v>198</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="50.1" customHeight="1">
       <c r="A74" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D74" s="17">
         <v>61464</v>
@@ -4153,22 +4156,22 @@
         <v>199</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="50.1" customHeight="1">
       <c r="A75" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D75" s="17">
         <v>61218</v>
       </c>
       <c r="E75" s="179"/>
       <c r="F75" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G75" s="1">
         <v>188</v>
@@ -4180,15 +4183,15 @@
         <v>188</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="50.1" customHeight="1">
       <c r="A76" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D76" s="17">
         <v>61434</v>
@@ -4207,22 +4210,22 @@
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="50.1" customHeight="1">
       <c r="A77" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D77" s="17">
         <v>61011</v>
       </c>
       <c r="E77" s="180"/>
       <c r="F77" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G77" s="1">
         <v>178</v>
@@ -4234,15 +4237,15 @@
         <v>178</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="50.1" customHeight="1">
       <c r="A78" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D78" s="17">
         <v>61357</v>
@@ -4261,15 +4264,15 @@
         <v>159</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="50.1" customHeight="1">
       <c r="A79" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D79" s="17">
         <v>61355</v>
@@ -4288,15 +4291,15 @@
         <v>172</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="50.1" customHeight="1">
       <c r="A80" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D80" s="17">
         <v>61465</v>
@@ -4315,15 +4318,15 @@
         <v>173</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="50.1" customHeight="1">
       <c r="A81" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D81" s="17">
         <v>61366</v>
@@ -4342,15 +4345,15 @@
         <v>135</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="50.1" customHeight="1">
       <c r="A82" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D82" s="17">
         <v>61379</v>
@@ -4369,15 +4372,15 @@
         <v>135</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="50.1" customHeight="1">
       <c r="A83" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D83" s="17">
         <v>61470</v>
@@ -4396,15 +4399,15 @@
         <v>130</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" ht="50.1" customHeight="1">
       <c r="A84" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D84" s="17">
         <v>61475</v>
@@ -4423,15 +4426,15 @@
         <v>144</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" ht="50.1" customHeight="1">
       <c r="A85" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D85" s="17">
         <v>61380</v>
@@ -4450,15 +4453,15 @@
         <v>122</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="50.1" customHeight="1">
       <c r="A86" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D86" s="17">
         <v>61356</v>
@@ -4477,15 +4480,15 @@
         <v>139</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="50.1" customHeight="1">
       <c r="A87" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D87" s="17">
         <v>61471</v>
@@ -4504,15 +4507,15 @@
         <v>145</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" ht="50.1" customHeight="1">
       <c r="A88" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D88" s="17">
         <v>61180</v>
@@ -4531,15 +4534,15 @@
         <v>98</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" ht="50.1" customHeight="1">
       <c r="A89" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D89" s="17">
         <v>61040</v>
@@ -4558,15 +4561,15 @@
         <v>113</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" ht="50.1" customHeight="1">
       <c r="A90" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D90" s="17">
         <v>61358</v>
@@ -4585,15 +4588,15 @@
         <v>113</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="50.1" customHeight="1">
       <c r="A91" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D91" s="17">
         <v>61463</v>
@@ -4612,15 +4615,15 @@
         <v>84</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" ht="50.1" customHeight="1">
       <c r="A92" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D92" s="17">
         <v>61041</v>
@@ -4639,15 +4642,15 @@
         <v>110</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" ht="50.1" customHeight="1">
       <c r="A93" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D93" s="17">
         <v>61353</v>
@@ -4666,22 +4669,22 @@
         <v>110</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" ht="50.1" customHeight="1">
       <c r="A94" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D94" s="17">
         <v>61219</v>
       </c>
       <c r="E94" s="178"/>
       <c r="F94" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G94" s="1">
         <v>99</v>
@@ -4693,15 +4696,15 @@
         <v>104</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="50.1" customHeight="1">
       <c r="A95" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D95" s="17">
         <v>61370</v>
@@ -4720,15 +4723,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" ht="50.1" customHeight="1">
       <c r="A96" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D96" s="17">
         <v>61385</v>
@@ -4747,15 +4750,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="50.1" customHeight="1">
       <c r="A97" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D97" s="17">
         <v>61059</v>
@@ -4774,15 +4777,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" ht="50.1" customHeight="1">
       <c r="A98" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D98" s="17">
         <v>61166</v>
@@ -4801,15 +4804,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="50.1" customHeight="1">
       <c r="A99" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D99" s="17">
         <v>61354</v>
@@ -4828,15 +4831,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="50.1" customHeight="1">
       <c r="A100" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D100" s="17">
         <v>61455</v>
@@ -4855,15 +4858,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="50.1" customHeight="1">
       <c r="A101" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D101" s="17">
         <v>61439</v>
@@ -4882,15 +4885,15 @@
         <v>68</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" ht="50.1" customHeight="1">
       <c r="A102" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D102" s="17">
         <v>61397</v>
@@ -4909,15 +4912,15 @@
         <v>44</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" ht="50.1" customHeight="1">
       <c r="A103" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D103" s="17">
         <v>61131</v>
@@ -4936,15 +4939,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" ht="50.1" customHeight="1">
       <c r="A104" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D104" s="17">
         <v>61005</v>
@@ -4963,15 +4966,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" ht="50.1" customHeight="1">
       <c r="A105" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D105" s="17">
         <v>61047</v>
@@ -4990,15 +4993,15 @@
         <v>142</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" ht="50.1" customHeight="1">
       <c r="A106" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D106" s="17">
         <v>61453</v>
@@ -5017,15 +5020,15 @@
         <v>142</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" ht="50.1" customHeight="1">
       <c r="A107" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D107" s="17">
         <v>61100</v>
@@ -5044,15 +5047,15 @@
         <v>129</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" ht="50.1" customHeight="1">
       <c r="A108" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D108" s="17">
         <v>61104</v>
@@ -5071,15 +5074,15 @@
         <v>124</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" ht="50.1" customHeight="1">
       <c r="A109" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D109" s="17">
         <v>61510</v>
@@ -5098,15 +5101,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" ht="50.1" customHeight="1">
       <c r="A110" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D110" s="17">
         <v>61446</v>
@@ -5125,15 +5128,15 @@
         <v>178</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" ht="50.1" customHeight="1">
       <c r="A111" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D111" s="17">
         <v>61049</v>
@@ -5152,15 +5155,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" ht="50.1" customHeight="1">
       <c r="A112" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D112" s="17">
         <v>61452</v>
@@ -5179,15 +5182,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" ht="50.1" customHeight="1">
       <c r="A113" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D113" s="17">
         <v>61177</v>
@@ -5206,15 +5209,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" ht="50.1" customHeight="1">
       <c r="A114" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D114" s="17">
         <v>61448</v>
@@ -5233,15 +5236,15 @@
         <v>92</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" ht="50.1" customHeight="1">
       <c r="A115" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D115" s="17">
         <v>61513</v>
@@ -5260,15 +5263,15 @@
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" ht="50.1" customHeight="1">
       <c r="A116" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D116" s="17">
         <v>61101</v>
@@ -5287,15 +5290,15 @@
         <v>55</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" ht="50.1" customHeight="1">
       <c r="A117" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D117" s="17">
         <v>61176</v>
@@ -5314,15 +5317,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" ht="50.1" customHeight="1">
       <c r="A118" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D118" s="17">
         <v>61443</v>
@@ -5341,15 +5344,15 @@
         <v>128</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" ht="50.1" customHeight="1">
       <c r="A119" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D119" s="17">
         <v>61079</v>
@@ -5368,15 +5371,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" ht="50.1" customHeight="1">
       <c r="A120" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D120" s="17">
         <v>61469</v>
@@ -5395,15 +5398,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" ht="50.1" customHeight="1">
       <c r="A121" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D121" s="17">
         <v>61442</v>
@@ -5422,15 +5425,15 @@
         <v>101</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" ht="50.1" customHeight="1">
       <c r="A122" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D122" s="17">
         <v>61173</v>
@@ -5449,15 +5452,15 @@
         <v>24</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" ht="50.1" customHeight="1">
       <c r="A123" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D123" s="17">
         <v>61051</v>
@@ -5476,15 +5479,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" ht="50.1" customHeight="1">
       <c r="A124" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D124" s="17">
         <v>61096</v>
@@ -5503,15 +5506,15 @@
         <v>126</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" ht="50.1" customHeight="1">
       <c r="A125" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D125" s="17">
         <v>61046</v>
@@ -5530,15 +5533,15 @@
         <v>97</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" ht="50.1" customHeight="1">
       <c r="A126" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D126" s="17">
         <v>61451</v>
@@ -5557,15 +5560,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" ht="50.1" customHeight="1">
       <c r="A127" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D127" s="17">
         <v>61230</v>
@@ -5584,15 +5587,15 @@
         <v>97</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" ht="50.1" customHeight="1">
       <c r="A128" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D128" s="17">
         <v>61208</v>
@@ -5611,15 +5614,15 @@
         <v>71</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" ht="50.1" customHeight="1">
       <c r="A129" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D129" s="17">
         <v>61444</v>
@@ -5638,15 +5641,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" ht="50.1" customHeight="1">
       <c r="A130" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D130" s="17">
         <v>61449</v>
@@ -5665,15 +5668,15 @@
         <v>63</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" ht="50.1" customHeight="1">
       <c r="A131" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D131" s="17">
         <v>61445</v>
@@ -5692,15 +5695,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" ht="50.1" customHeight="1">
       <c r="A132" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D132" s="17">
         <v>61174</v>
@@ -5719,15 +5722,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" ht="50.1" customHeight="1">
       <c r="A133" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D133" s="17">
         <v>61175</v>
@@ -5746,15 +5749,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" ht="50.1" customHeight="1">
       <c r="A134" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D134" s="17">
         <v>61103</v>
@@ -5773,15 +5776,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" ht="50.1" customHeight="1">
       <c r="A135" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D135" s="17">
         <v>61454</v>
@@ -5800,15 +5803,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" ht="50.1" customHeight="1">
       <c r="A136" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D136" s="17">
         <v>61171</v>
@@ -5827,15 +5830,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" ht="50.1" customHeight="1">
       <c r="A137" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D137" s="17">
         <v>61367</v>
@@ -5854,22 +5857,22 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" ht="50.1" customHeight="1">
       <c r="A138" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D138" s="17">
         <v>61078</v>
       </c>
       <c r="E138" s="175"/>
       <c r="F138" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G138" s="1">
         <v>255</v>
@@ -5881,15 +5884,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" ht="50.1" customHeight="1">
       <c r="A139" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D139" s="17">
         <v>61113</v>
@@ -5908,15 +5911,15 @@
         <v>207</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" ht="50.1" customHeight="1">
       <c r="A140" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D140" s="17">
         <v>61111</v>
@@ -5935,15 +5938,15 @@
         <v>215</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" ht="50.1" customHeight="1">
       <c r="A141" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D141" s="17">
         <v>61258</v>
@@ -5962,15 +5965,15 @@
         <v>157</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" ht="50.1" customHeight="1">
       <c r="A142" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D142" s="17">
         <v>61117</v>
@@ -5989,15 +5992,15 @@
         <v>202</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" ht="50.1" customHeight="1">
       <c r="A143" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D143" s="17">
         <v>61225</v>
@@ -6016,15 +6019,15 @@
         <v>196</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" ht="50.1" customHeight="1">
       <c r="A144" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D144" s="17">
         <v>61108</v>
@@ -6043,15 +6046,15 @@
         <v>188</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" ht="50.1" customHeight="1">
       <c r="A145" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D145" s="17">
         <v>61115</v>
@@ -6070,15 +6073,15 @@
         <v>188</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" ht="50.1" customHeight="1">
       <c r="A146" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D146" s="17">
         <v>61224</v>
@@ -6097,15 +6100,15 @@
         <v>200</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" ht="50.1" customHeight="1">
       <c r="A147" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D147" s="17">
         <v>61410</v>
@@ -6124,15 +6127,15 @@
         <v>200</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" ht="50.1" customHeight="1">
       <c r="A148" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D148" s="17">
         <v>61148</v>
@@ -6151,15 +6154,15 @@
         <v>178</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" ht="50.1" customHeight="1">
       <c r="A149" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D149" s="17">
         <v>61394</v>
@@ -6178,15 +6181,15 @@
         <v>172</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" ht="50.1" customHeight="1">
       <c r="A150" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D150" s="17">
         <v>61020</v>
@@ -6205,15 +6208,15 @@
         <v>136</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" ht="50.1" customHeight="1">
       <c r="A151" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D151" s="17">
         <v>61054</v>
@@ -6232,15 +6235,15 @@
         <v>132</v>
       </c>
     </row>
-    <row r="152" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" ht="50.1" customHeight="1">
       <c r="A152" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D152" s="17">
         <v>61259</v>
@@ -6259,15 +6262,15 @@
         <v>111</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" ht="50.1" customHeight="1">
       <c r="A153" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D153" s="17">
         <v>61109</v>
@@ -6286,15 +6289,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" ht="50.1" customHeight="1">
       <c r="A154" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D154" s="17">
         <v>61511</v>
@@ -6313,15 +6316,15 @@
         <v>150</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" ht="50.1" customHeight="1">
       <c r="A155" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D155" s="17">
         <v>61418</v>
@@ -6340,15 +6343,15 @@
         <v>223</v>
       </c>
     </row>
-    <row r="156" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" ht="50.1" customHeight="1">
       <c r="A156" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D156" s="17">
         <v>61031</v>
@@ -6367,15 +6370,15 @@
         <v>206</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" ht="50.1" customHeight="1">
       <c r="A157" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D157" s="17">
         <v>61032</v>
@@ -6394,15 +6397,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" ht="50.1" customHeight="1">
       <c r="A158" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D158" s="17">
         <v>61417</v>
@@ -6421,15 +6424,15 @@
         <v>191</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" ht="50.1" customHeight="1">
       <c r="A159" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D159" s="17">
         <v>61231</v>
@@ -6448,15 +6451,15 @@
         <v>130</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" ht="50.1" customHeight="1">
       <c r="A160" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D160" s="17">
         <v>61191</v>
@@ -6475,15 +6478,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" ht="50.1" customHeight="1">
       <c r="A161" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D161" s="17">
         <v>61033</v>
@@ -6502,15 +6505,15 @@
         <v>152</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" ht="50.1" customHeight="1">
       <c r="A162" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D162" s="17">
         <v>61533</v>
@@ -6529,15 +6532,15 @@
         <v>95</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" ht="50.1" customHeight="1">
       <c r="A163" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D163" s="17">
         <v>61406</v>
@@ -6556,15 +6559,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="164" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" ht="50.1" customHeight="1">
       <c r="A164" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D164" s="17">
         <v>61195</v>
@@ -6583,15 +6586,15 @@
         <v>156</v>
       </c>
     </row>
-    <row r="165" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" ht="50.1" customHeight="1">
       <c r="A165" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D165" s="17">
         <v>61412</v>
@@ -6610,15 +6613,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" ht="50.1" customHeight="1">
       <c r="A166" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D166" s="17">
         <v>61409</v>
@@ -6637,15 +6640,15 @@
         <v>82</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" ht="50.1" customHeight="1">
       <c r="A167" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D167" s="17">
         <v>61405</v>
@@ -6664,15 +6667,15 @@
         <v>69</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" ht="50.1" customHeight="1">
       <c r="A168" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D168" s="17">
         <v>61411</v>
@@ -6691,15 +6694,15 @@
         <v>101</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" ht="50.1" customHeight="1">
       <c r="A169" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D169" s="17">
         <v>61407</v>
@@ -6718,15 +6721,15 @@
         <v>68</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" ht="50.1" customHeight="1">
       <c r="A170" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D170" s="17">
         <v>61413</v>
@@ -6745,15 +6748,15 @@
         <v>93</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" ht="50.1" customHeight="1">
       <c r="A171" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D171" s="17">
         <v>61423</v>
@@ -6772,15 +6775,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" ht="50.1" customHeight="1">
       <c r="A172" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D172" s="17">
         <v>61034</v>
@@ -6799,22 +6802,22 @@
         <v>95</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" ht="50.1" customHeight="1">
       <c r="A173" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D173" s="17">
         <v>61184</v>
       </c>
       <c r="E173" s="181"/>
       <c r="F173" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G173" s="1">
         <v>254</v>
@@ -6826,15 +6829,15 @@
         <v>53</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" ht="50.1" customHeight="1">
       <c r="A174" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D174" s="17">
         <v>61078</v>
@@ -6853,15 +6856,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" ht="50.1" customHeight="1">
       <c r="A175" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D175" s="17">
         <v>61457</v>
@@ -6880,15 +6883,15 @@
         <v>22</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" ht="50.1" customHeight="1">
       <c r="A176" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D176" s="17">
         <v>61037</v>
@@ -6907,15 +6910,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" ht="50.1" customHeight="1">
       <c r="A177" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D177" s="17">
         <v>61147</v>
@@ -6934,15 +6937,15 @@
         <v>41</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" ht="50.1" customHeight="1">
       <c r="A178" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D178" s="17">
         <v>61181</v>
@@ -6961,15 +6964,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" ht="50.1" customHeight="1">
       <c r="A179" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D179" s="17">
         <v>61181</v>
@@ -6988,15 +6991,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" ht="50.1" customHeight="1">
       <c r="A180" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D180" s="17">
         <v>61039</v>
@@ -7015,15 +7018,15 @@
         <v>58</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" ht="50.1" customHeight="1">
       <c r="A181" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D181" s="17">
         <v>61398</v>
@@ -7042,15 +7045,15 @@
         <v>45</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" ht="50.1" customHeight="1">
       <c r="A182" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D182" s="17">
         <v>61390</v>
@@ -7069,15 +7072,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" ht="50.1" customHeight="1">
       <c r="A183" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D183" s="17">
         <v>61395</v>
@@ -7096,15 +7099,15 @@
         <v>42</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" ht="50.1" customHeight="1">
       <c r="A184" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D184" s="17">
         <v>61401</v>
@@ -7123,15 +7126,15 @@
         <v>51</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" ht="50.1" customHeight="1">
       <c r="A185" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D185" s="17">
         <v>61169</v>
@@ -7150,15 +7153,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" ht="50.1" customHeight="1">
       <c r="A186" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D186" s="17">
         <v>61594</v>
@@ -7177,15 +7180,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" ht="50.1" customHeight="1">
       <c r="A187" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D187" s="17">
         <v>61035</v>
@@ -7204,22 +7207,22 @@
         <v>60</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" ht="50.1" customHeight="1">
       <c r="A188" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D188" s="17">
         <v>61351</v>
       </c>
       <c r="E188" s="183"/>
       <c r="F188" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G188" s="1">
         <v>0</v>
@@ -7231,15 +7234,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" ht="50.1" customHeight="1">
       <c r="A189" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D189" s="17">
         <v>61067</v>
@@ -7258,15 +7261,15 @@
         <v>94</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" ht="50.1" customHeight="1">
       <c r="A190" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D190" s="17">
         <v>61135</v>
@@ -7285,15 +7288,15 @@
         <v>79</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" ht="50.1" customHeight="1">
       <c r="A191" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D191" s="17">
         <v>61187</v>
@@ -7312,15 +7315,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" ht="50.1" customHeight="1">
       <c r="A192" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D192" s="17">
         <v>61456</v>
@@ -7339,15 +7342,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" ht="50.1" customHeight="1">
       <c r="A193" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D193" s="17">
         <v>61023</v>
@@ -7366,15 +7369,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" ht="50.1" customHeight="1">
       <c r="A194" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D194" s="17">
         <v>61365</v>
@@ -7393,15 +7396,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" ht="50.1" customHeight="1">
       <c r="A195" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D195" s="17">
         <v>61124</v>
@@ -7420,15 +7423,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" ht="50.1" customHeight="1">
       <c r="A196" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D196" s="17">
         <v>61359</v>
@@ -7447,15 +7450,15 @@
         <v>47</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" ht="50.1" customHeight="1">
       <c r="A197" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D197" s="17">
         <v>61167</v>
@@ -7474,15 +7477,15 @@
         <v>80</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" ht="50.1" customHeight="1">
       <c r="A198" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D198" s="17">
         <v>61185</v>
@@ -7501,15 +7504,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" ht="50.1" customHeight="1">
       <c r="A199" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D199" s="17">
         <v>61083</v>
@@ -7528,15 +7531,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" ht="50.1" customHeight="1">
       <c r="A200" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D200" s="17">
         <v>61368</v>
@@ -7555,15 +7558,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" ht="50.1" customHeight="1">
       <c r="A201" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D201" s="17">
         <v>61159</v>
@@ -7582,30 +7585,251 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="5:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="5:5" ht="50.1" hidden="1" customHeight="1">
       <c r="E280" s="16"/>
     </row>
-    <row r="289" spans="5:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="5:5" ht="50.1" hidden="1" customHeight="1">
       <c r="E289" s="32"/>
     </row>
-    <row r="297" spans="5:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="5:5" ht="50.1" hidden="1" customHeight="1">
       <c r="E297" s="31"/>
     </row>
-    <row r="352" spans="5:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="5:5" ht="50.1" hidden="1" customHeight="1">
       <c r="E352" s="31"/>
     </row>
-    <row r="367" spans="5:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="5:5" ht="50.1" hidden="1" customHeight="1">
       <c r="E367" s="32"/>
     </row>
-    <row r="407" spans="5:5" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="5:5" ht="50.1" hidden="1" customHeight="1">
       <c r="E407" s="16"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="BtrAD98WMdw4zg0BM9uSqKK58LZoh/fsq/+fUzqwolCrke2GqelJbR6+hqDqNyneAh3tN31W5WeezrNY9nbzIw==" saltValue="GM/buCkB9mK7xHlYJBw2/Q==" spinCount="100000" sheet="1" objects="1" scenarios="1" sort="0" autoFilter="0"/>
+  <sheetProtection sort="0" autoFilter="0"/>
   <protectedRanges>
     <protectedRange sqref="A1:I201" name="AllowSortFilter"/>
   </protectedRanges>
   <autoFilter ref="A1:I1" xr:uid="{FE7DE5AC-E6A0-4E0D-9AE8-E8E89420A822}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea7a09a4-fe73-437e-8a86-996460e9b058">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A1C7DD37AE641E4B9B3FD2F75B2D99BC" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="6b9cb41f595aff4764e09aef2b23c1ed">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ea7a09a4-fe73-437e-8a86-996460e9b058" xmlns:ns3="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="daad8a4a6daff5298e6b89d91afce8e3" ns2:_="" ns3:_="">
+    <xsd:import namespace="ea7a09a4-fe73-437e-8a86-996460e9b058"/>
+    <xsd:import namespace="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="ea7a09a4-fe73-437e-8a86-996460e9b058" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="d2f5926c-fefe-46c4-85d9-9ef0eea46f5c" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{6fbb2a74-2168-4404-a595-59f9a11d4eed}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="a2b9d960-66d6-4e1d-a64a-950bc94b8bb0">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88945697-E3C2-434F-82CF-7A35A72E0851}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7999096-FDAC-4002-81A0-B811A35F3D54}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1553275E-4B48-42CD-B5C0-C9014E83EB93}"/>
 </file>